--- a/backtest_runs/20260410_193731/by_symbol/DSIL/DSIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DSIL/DSIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-3605.020000000007</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99373.03999999998</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>99373.03999999998</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>107680.26</v>
@@ -909,7 +909,7 @@
         <v>-2978.059999999992</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>104702.2</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>104702.2</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>104702.2</v>
@@ -1231,7 +1231,7 @@
         <v>-470.2200000000039</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>110501.58</v>
@@ -1277,7 +1277,7 @@
         <v>-9404.399999999994</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>101097.18</v>
@@ -1415,7 +1415,7 @@
         <v>-1880.880000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>107053.3</v>
@@ -1461,7 +1461,7 @@
         <v>-2194.360000000009</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>104858.94</v>
@@ -1645,7 +1645,7 @@
         <v>-6426.340000000002</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>107366.78</v>
